--- a/diseases/d231/2010-2014.xlsx
+++ b/diseases/d231/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d231/2010-2014.xlsx
+++ b/diseases/d231/2010-2014.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12884,7 +12884,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14468,7 +14468,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16448,7 +16448,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16844,7 +16844,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17240,7 +17240,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17636,7 +17636,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18032,7 +18032,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18428,7 +18428,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19220,7 +19220,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20012,7 +20012,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20408,7 +20408,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21596,7 +21596,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21992,7 +21992,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22388,7 +22388,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22784,7 +22784,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24368,7 +24368,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d231/2010-2014.xlsx
+++ b/diseases/d231/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>472</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.2436733600013004</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>434</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.2240555894927211</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>558</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.2880714722049271</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>458</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.2364457603402448</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>477</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.2462546455945344</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>420</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.2168279898316656</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>504</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2601935877979987</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>520</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.2684537016963478</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>523</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.2700024730522883</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>511</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.2638073876285265</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>536</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.276713815594697</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>473</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.2441896171199472</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>503</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.257572616358295</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>692</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.3543543747911335</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>587</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.3005867312173344</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>532</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.2724227274405824</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>618</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.3164609878915036</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>587</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.3005867312173344</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>500</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.2560363979704722</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>612</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.3133885511158579</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>529</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.2708865090527596</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>500</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.2560363979704722</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>574</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.2939297848701021</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>538</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.2754951642162281</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>590</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2996808477700962</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>535</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.2717444975542398</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>669</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.3398076053528719</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>591</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.3001887814103846</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>658</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.3342203353097006</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>534</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.2712365639139515</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>564</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.2864745731226005</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>641</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.3255854634247995</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>550</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.2793635021585643</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>613</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.3113633214967271</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>558</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.2834269712808707</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>470</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.2387288109355004</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>630</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.3174150532260077</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>530</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.2670317114441017</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>633</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.3189265534794649</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>686</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.345629724623875</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>563</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.2836582142321307</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>635</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.319934220315103</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>690</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.3476450582951513</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>701</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.3531872258911609</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>631</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.3179188866438268</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>601</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.302803884109255</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>554</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.2791237134717592</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>493</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.2483898749847965</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>621</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.3103678965603475</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>628</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.3138664074716558</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>582</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.29087619291163</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>612</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.3058698111029512</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>647</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.3233623656594925</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>591</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.2953742783690264</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>733</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.3663440711412798</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>714</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.356848112953443</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>706</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.3528498147690908</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>681</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.3403551329429898</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>575</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.2873776820003218</v>
       </c>
@@ -24128,9 +23951,6 @@
       </c>
       <c r="O120" t="n">
         <v>604</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.3018715129185989</v>

--- a/diseases/d231/2010-2014.xlsx
+++ b/diseases/d231/2010-2014.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d231/2010-2014.xlsx
+++ b/diseases/d231/2010-2014.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d231/2010-2014.xlsx
+++ b/diseases/d231/2010-2014.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">

--- a/diseases/d231/2010-2014.xlsx
+++ b/diseases/d231/2010-2014.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13184,7 +13184,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13577,7 +13577,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14363,7 +14363,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -14756,7 +14756,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16328,7 +16328,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -16721,7 +16721,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -17900,7 +17900,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
